--- a/reports/集团总公司_利润表_2026-08.xlsx
+++ b/reports/集团总公司_利润表_2026-08.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>241880638</v>
+        <v>264290175</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>192712758</v>
+        <v>208451262</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1359956608</v>
+        <v>1477927789</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>785994</v>
+        <v>1015249</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>5645644</v>
+        <v>7304908</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>679414</v>
+        <v>889906</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>4896320</v>
+        <v>6392694</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>576034</v>
+        <v>752253</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>4151087</v>
+        <v>5397112</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>531795</v>
+        <v>694967</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>3820078</v>
+        <v>4982435</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>288570</v>
+        <v>382275</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>2075121</v>
+        <v>2740480</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>230168</v>
+        <v>301020</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1659893</v>
+        <v>2159156</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>238788663</v>
+        <v>260254505</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>189620783</v>
+        <v>204415592</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>97466321</v>
+        <v>106887803</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>676752348</v>
+        <v>743527487</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1786074</v>
+        <v>3163113</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>12867136</v>
+        <v>22826089</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1617912</v>
+        <v>2298216</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>11626862</v>
+        <v>16599295</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>86816916</v>
+        <v>90624621</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>622594421</v>
+        <v>655549539</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1838353</v>
+        <v>2298203</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>13274420</v>
+        <v>16597664</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>806700</v>
+        <v>1151203</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>5812432</v>
+        <v>8299790</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2897723</v>
+        <v>3459465</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>20766629</v>
+        <v>24901780</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1268833</v>
+        <v>1731751</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>9129496</v>
+        <v>12452234</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>48986329</v>
+        <v>49524001</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>422955723</v>
+        <v>423227427</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>181551</v>
+        <v>175791</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>1404653</v>
+        <v>1401214</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3683838</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>26407762</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2455283</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>17605556</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>191721579</v>
+        <v>216189426</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>151533453</v>
+        <v>159743080</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>120447138</v>
+        <v>128653644</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>840898884</v>
+        <v>899787865</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>31086315</v>
+        <v>31089436</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>224816521</v>
+        <v>224888036</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>6094015</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>43991493</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1948539</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>14075941</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1217747</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>8797057</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1462258</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>10556584</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>1098092</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>7917962</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>733280</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>5279218</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>612142</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>4399937</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>3397534</v>
+        <v>3414401</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>24494871</v>
+        <v>24495002</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1608147</v>
+        <v>1609177</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>11543950</v>
+        <v>11541543</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>4154353</v>
+        <v>4166835</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>29873305</v>
+        <v>29895962</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>31049604</v>
+        <v>31261588</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>203175754</v>
+        <v>203393073</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>385468</v>
+        <v>3283421</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>2897249</v>
+        <v>23660610</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1201167</v>
+        <v>1154028</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>9252944</v>
+        <v>9228561</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1241557</v>
+        <v>1102196</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>9577777</v>
+        <v>8816482</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>129472</v>
+        <v>123375</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>991827</v>
+        <v>988621</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>489628</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>3929375</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>1065551</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>7697710</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>326197</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>2619570</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>244831</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1964824</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>408600</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>3275078</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1528026</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>10998558</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>218670</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1747152</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>164249</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1310493</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>274016</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>2184269</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>191869</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1528984</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>136988</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>1092069</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>109470</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>873571</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>81973</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>655096</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>47067084</v>
+        <v>47696203</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>67747049</v>
+        <v>67301610</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>609234</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>4399023</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>135907</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>1091461</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>225560</v>
+        <v>215429</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1735131</v>
+        <v>1729920</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>46841524</v>
+        <v>48090008</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7673208</v>
+        <v>7298100</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>58673568</v>
+        <v>58498192</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>39168316</v>
+        <v>40791908</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>39168316</v>
+        <v>40791908</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>39168316</v>
+        <v>40791908</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>39168316</v>
+        <v>40791908</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>39168316</v>
+        <v>40791908</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
